--- a/woodland.xlsx
+++ b/woodland.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C148B4B6-EB77-42E2-A3E5-308AE5977B9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C6902032-8390-4788-BEBB-EFAFD9CBE80D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4092" uniqueCount="722">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4100" uniqueCount="723">
   <si>
     <t>Scheme Listing by CRID for ZIP Code 98674</t>
   </si>
@@ -1694,6 +1694,9 @@
     <t>NIEMI</t>
   </si>
   <si>
+    <t>OLD GREEN MOUNTAIN</t>
+  </si>
+  <si>
     <t>2800</t>
   </si>
   <si>
@@ -2177,7 +2180,7 @@
     <t>YORK</t>
   </si>
   <si>
-    <t>Total Line items: 510</t>
+    <t>Total Line items: 511</t>
   </si>
   <si>
     <t>zip code</t>
@@ -2578,7 +2581,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I513"/>
+  <dimension ref="A1:I514"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="3" width="8" customWidth="1"/>
@@ -2616,7 +2619,7 @@
       <c r="F2" s="5"/>
       <c r="G2" s="5"/>
       <c r="H2" s="2" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="I2" s="2" t="s">
         <v>4</v>
@@ -13383,20 +13386,20 @@
     </row>
     <row r="374" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A374" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="B374" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="C374" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D374" t="s">
+        <v>11</v>
+      </c>
+      <c r="E374" t="s">
         <v>559</v>
       </c>
-      <c r="B374" s="3" t="s">
-        <v>560</v>
-      </c>
-      <c r="C374" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D374" t="s">
-        <v>11</v>
-      </c>
-      <c r="E374" t="s">
-        <v>561</v>
-      </c>
       <c r="F374" t="s">
         <v>240</v>
       </c>
@@ -13407,15 +13410,15 @@
         <v>98674</v>
       </c>
       <c r="I374" s="1" t="s">
-        <v>249</v>
+        <v>260</v>
       </c>
     </row>
     <row r="375" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A375" s="3" t="s">
-        <v>205</v>
+        <v>560</v>
       </c>
       <c r="B375" s="3" t="s">
-        <v>196</v>
+        <v>561</v>
       </c>
       <c r="C375" s="1" t="s">
         <v>7</v>
@@ -13424,7 +13427,7 @@
         <v>11</v>
       </c>
       <c r="E375" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="F375" t="s">
         <v>240</v>
@@ -13436,24 +13439,24 @@
         <v>98674</v>
       </c>
       <c r="I375" s="1" t="s">
-        <v>237</v>
+        <v>249</v>
       </c>
     </row>
     <row r="376" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A376" s="3" t="s">
-        <v>146</v>
+        <v>205</v>
       </c>
       <c r="B376" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="C376" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D376" t="s">
+        <v>11</v>
+      </c>
+      <c r="E376" t="s">
         <v>562</v>
-      </c>
-      <c r="C376" s="1" t="s">
-        <v>283</v>
-      </c>
-      <c r="D376" t="s">
-        <v>11</v>
-      </c>
-      <c r="E376" t="s">
-        <v>561</v>
       </c>
       <c r="F376" t="s">
         <v>240</v>
@@ -13470,19 +13473,19 @@
     </row>
     <row r="377" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A377" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="B377" s="3" t="s">
         <v>563</v>
       </c>
-      <c r="B377" s="3" t="s">
-        <v>191</v>
-      </c>
       <c r="C377" s="1" t="s">
-        <v>114</v>
+        <v>283</v>
       </c>
       <c r="D377" t="s">
         <v>11</v>
       </c>
       <c r="E377" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="F377" t="s">
         <v>240</v>
@@ -13494,7 +13497,7 @@
         <v>98674</v>
       </c>
       <c r="I377" s="1" t="s">
-        <v>273</v>
+        <v>237</v>
       </c>
     </row>
     <row r="378" spans="1:9" x14ac:dyDescent="0.35">
@@ -13502,16 +13505,16 @@
         <v>564</v>
       </c>
       <c r="B378" s="3" t="s">
-        <v>147</v>
+        <v>191</v>
       </c>
       <c r="C378" s="1" t="s">
-        <v>7</v>
+        <v>114</v>
       </c>
       <c r="D378" t="s">
         <v>11</v>
       </c>
       <c r="E378" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="F378" t="s">
         <v>240</v>
@@ -13531,7 +13534,7 @@
         <v>565</v>
       </c>
       <c r="B379" s="3" t="s">
-        <v>421</v>
+        <v>147</v>
       </c>
       <c r="C379" s="1" t="s">
         <v>7</v>
@@ -13540,10 +13543,10 @@
         <v>11</v>
       </c>
       <c r="E379" t="s">
-        <v>566</v>
+        <v>562</v>
       </c>
       <c r="F379" t="s">
-        <v>567</v>
+        <v>240</v>
       </c>
       <c r="G379" t="s">
         <v>11</v>
@@ -13552,28 +13555,28 @@
         <v>98674</v>
       </c>
       <c r="I379" s="1" t="s">
-        <v>20</v>
+        <v>273</v>
       </c>
     </row>
     <row r="380" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A380" s="3" t="s">
+        <v>566</v>
+      </c>
+      <c r="B380" s="3" t="s">
+        <v>421</v>
+      </c>
+      <c r="C380" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D380" t="s">
+        <v>11</v>
+      </c>
+      <c r="E380" t="s">
+        <v>567</v>
+      </c>
+      <c r="F380" t="s">
         <v>568</v>
       </c>
-      <c r="B380" s="3" t="s">
-        <v>569</v>
-      </c>
-      <c r="C380" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D380" t="s">
-        <v>11</v>
-      </c>
-      <c r="E380" t="s">
-        <v>566</v>
-      </c>
-      <c r="F380" t="s">
-        <v>567</v>
-      </c>
       <c r="G380" t="s">
         <v>11</v>
       </c>
@@ -13581,27 +13584,27 @@
         <v>98674</v>
       </c>
       <c r="I380" s="1" t="s">
-        <v>260</v>
+        <v>20</v>
       </c>
     </row>
     <row r="381" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A381" s="3" t="s">
+        <v>569</v>
+      </c>
+      <c r="B381" s="3" t="s">
         <v>570</v>
       </c>
-      <c r="B381" s="3" t="s">
-        <v>571</v>
-      </c>
       <c r="C381" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D381" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E381" t="s">
-        <v>572</v>
+        <v>567</v>
       </c>
       <c r="F381" t="s">
-        <v>240</v>
+        <v>568</v>
       </c>
       <c r="G381" t="s">
         <v>11</v>
@@ -13610,21 +13613,21 @@
         <v>98674</v>
       </c>
       <c r="I381" s="1" t="s">
-        <v>12</v>
+        <v>260</v>
       </c>
     </row>
     <row r="382" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A382" s="3" t="s">
-        <v>280</v>
+        <v>571</v>
       </c>
       <c r="B382" s="3" t="s">
-        <v>35</v>
+        <v>572</v>
       </c>
       <c r="C382" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D382" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E382" t="s">
         <v>573</v>
@@ -13639,15 +13642,15 @@
         <v>98674</v>
       </c>
       <c r="I382" s="1" t="s">
-        <v>237</v>
+        <v>12</v>
       </c>
     </row>
     <row r="383" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A383" s="3" t="s">
-        <v>153</v>
+        <v>280</v>
       </c>
       <c r="B383" s="3" t="s">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="C383" s="1" t="s">
         <v>7</v>
@@ -13676,7 +13679,7 @@
         <v>153</v>
       </c>
       <c r="B384" s="3" t="s">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="C384" s="1" t="s">
         <v>7</v>
@@ -13702,10 +13705,10 @@
     </row>
     <row r="385" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A385" s="3" t="s">
-        <v>233</v>
+        <v>153</v>
       </c>
       <c r="B385" s="3" t="s">
-        <v>257</v>
+        <v>37</v>
       </c>
       <c r="C385" s="1" t="s">
         <v>7</v>
@@ -13717,7 +13720,7 @@
         <v>576</v>
       </c>
       <c r="F385" t="s">
-        <v>10</v>
+        <v>240</v>
       </c>
       <c r="G385" t="s">
         <v>11</v>
@@ -13726,27 +13729,27 @@
         <v>98674</v>
       </c>
       <c r="I385" s="1" t="s">
-        <v>17</v>
+        <v>237</v>
       </c>
     </row>
     <row r="386" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A386" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="B386" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="C386" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D386" t="s">
+        <v>11</v>
+      </c>
+      <c r="E386" t="s">
         <v>577</v>
       </c>
-      <c r="B386" s="3" t="s">
-        <v>477</v>
-      </c>
-      <c r="C386" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D386" t="s">
-        <v>23</v>
-      </c>
-      <c r="E386" t="s">
-        <v>576</v>
-      </c>
       <c r="F386" t="s">
-        <v>567</v>
+        <v>10</v>
       </c>
       <c r="G386" t="s">
         <v>11</v>
@@ -13755,27 +13758,27 @@
         <v>98674</v>
       </c>
       <c r="I386" s="1" t="s">
-        <v>46</v>
+        <v>17</v>
       </c>
     </row>
     <row r="387" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A387" s="3" t="s">
-        <v>280</v>
+        <v>578</v>
       </c>
       <c r="B387" s="3" t="s">
-        <v>241</v>
+        <v>477</v>
       </c>
       <c r="C387" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D387" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="E387" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="F387" t="s">
-        <v>240</v>
+        <v>568</v>
       </c>
       <c r="G387" t="s">
         <v>11</v>
@@ -13784,12 +13787,12 @@
         <v>98674</v>
       </c>
       <c r="I387" s="1" t="s">
-        <v>260</v>
+        <v>46</v>
       </c>
     </row>
     <row r="388" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A388" s="3" t="s">
-        <v>153</v>
+        <v>280</v>
       </c>
       <c r="B388" s="3" t="s">
         <v>241</v>
@@ -13813,27 +13816,27 @@
         <v>98674</v>
       </c>
       <c r="I388" s="1" t="s">
-        <v>237</v>
+        <v>260</v>
       </c>
     </row>
     <row r="389" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A389" s="3" t="s">
-        <v>24</v>
+        <v>153</v>
       </c>
       <c r="B389" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="C389" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D389" t="s">
+        <v>11</v>
+      </c>
+      <c r="E389" t="s">
         <v>580</v>
       </c>
-      <c r="C389" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D389" t="s">
-        <v>11</v>
-      </c>
-      <c r="E389" t="s">
-        <v>581</v>
-      </c>
       <c r="F389" t="s">
-        <v>16</v>
+        <v>240</v>
       </c>
       <c r="G389" t="s">
         <v>11</v>
@@ -13842,24 +13845,24 @@
         <v>98674</v>
       </c>
       <c r="I389" s="1" t="s">
-        <v>20</v>
+        <v>237</v>
       </c>
     </row>
     <row r="390" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A390" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B390" s="3" t="s">
+        <v>581</v>
+      </c>
+      <c r="C390" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D390" t="s">
+        <v>11</v>
+      </c>
+      <c r="E390" t="s">
         <v>582</v>
-      </c>
-      <c r="B390" s="3" t="s">
-        <v>583</v>
-      </c>
-      <c r="C390" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D390" t="s">
-        <v>11</v>
-      </c>
-      <c r="E390" t="s">
-        <v>581</v>
       </c>
       <c r="F390" t="s">
         <v>16</v>
@@ -13871,16 +13874,16 @@
         <v>98674</v>
       </c>
       <c r="I390" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="391" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A391" s="3" t="s">
+        <v>583</v>
+      </c>
+      <c r="B391" s="3" t="s">
         <v>584</v>
       </c>
-      <c r="B391" s="3" t="s">
-        <v>265</v>
-      </c>
       <c r="C391" s="1" t="s">
         <v>7</v>
       </c>
@@ -13888,7 +13891,7 @@
         <v>11</v>
       </c>
       <c r="E391" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="F391" t="s">
         <v>16</v>
@@ -13900,15 +13903,15 @@
         <v>98674</v>
       </c>
       <c r="I391" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="392" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A392" s="3" t="s">
-        <v>153</v>
+        <v>585</v>
       </c>
       <c r="B392" s="3" t="s">
-        <v>25</v>
+        <v>265</v>
       </c>
       <c r="C392" s="1" t="s">
         <v>7</v>
@@ -13917,10 +13920,10 @@
         <v>11</v>
       </c>
       <c r="E392" t="s">
-        <v>585</v>
+        <v>582</v>
       </c>
       <c r="F392" t="s">
-        <v>240</v>
+        <v>16</v>
       </c>
       <c r="G392" t="s">
         <v>11</v>
@@ -13929,7 +13932,7 @@
         <v>98674</v>
       </c>
       <c r="I392" s="1" t="s">
-        <v>273</v>
+        <v>20</v>
       </c>
     </row>
     <row r="393" spans="1:9" x14ac:dyDescent="0.35">
@@ -13937,7 +13940,7 @@
         <v>153</v>
       </c>
       <c r="B393" s="3" t="s">
-        <v>241</v>
+        <v>25</v>
       </c>
       <c r="C393" s="1" t="s">
         <v>7</v>
@@ -13949,7 +13952,7 @@
         <v>586</v>
       </c>
       <c r="F393" t="s">
-        <v>27</v>
+        <v>240</v>
       </c>
       <c r="G393" t="s">
         <v>11</v>
@@ -13958,7 +13961,7 @@
         <v>98674</v>
       </c>
       <c r="I393" s="1" t="s">
-        <v>20</v>
+        <v>273</v>
       </c>
     </row>
     <row r="394" spans="1:9" x14ac:dyDescent="0.35">
@@ -13966,19 +13969,19 @@
         <v>153</v>
       </c>
       <c r="B394" s="3" t="s">
-        <v>14</v>
+        <v>241</v>
       </c>
       <c r="C394" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D394" t="s">
-        <v>305</v>
+        <v>11</v>
       </c>
       <c r="E394" t="s">
         <v>587</v>
       </c>
       <c r="F394" t="s">
-        <v>240</v>
+        <v>27</v>
       </c>
       <c r="G394" t="s">
         <v>11</v>
@@ -13995,16 +13998,16 @@
         <v>153</v>
       </c>
       <c r="B395" s="3" t="s">
-        <v>401</v>
+        <v>14</v>
       </c>
       <c r="C395" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D395" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="E395" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="F395" t="s">
         <v>240</v>
@@ -14016,15 +14019,15 @@
         <v>98674</v>
       </c>
       <c r="I395" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="396" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A396" s="3" t="s">
-        <v>588</v>
+        <v>153</v>
       </c>
       <c r="B396" s="3" t="s">
-        <v>589</v>
+        <v>401</v>
       </c>
       <c r="C396" s="1" t="s">
         <v>7</v>
@@ -14033,7 +14036,7 @@
         <v>306</v>
       </c>
       <c r="E396" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="F396" t="s">
         <v>240</v>
@@ -14050,22 +14053,22 @@
     </row>
     <row r="397" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A397" s="3" t="s">
-        <v>24</v>
+        <v>589</v>
       </c>
       <c r="B397" s="3" t="s">
-        <v>35</v>
+        <v>590</v>
       </c>
       <c r="C397" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D397" t="s">
-        <v>11</v>
+        <v>306</v>
       </c>
       <c r="E397" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="F397" t="s">
-        <v>16</v>
+        <v>240</v>
       </c>
       <c r="G397" t="s">
         <v>11</v>
@@ -14074,15 +14077,15 @@
         <v>98674</v>
       </c>
       <c r="I397" s="1" t="s">
-        <v>260</v>
+        <v>17</v>
       </c>
     </row>
     <row r="398" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A398" s="3" t="s">
-        <v>153</v>
+        <v>24</v>
       </c>
       <c r="B398" s="3" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="C398" s="1" t="s">
         <v>7</v>
@@ -14094,7 +14097,7 @@
         <v>591</v>
       </c>
       <c r="F398" t="s">
-        <v>243</v>
+        <v>16</v>
       </c>
       <c r="G398" t="s">
         <v>11</v>
@@ -14103,7 +14106,7 @@
         <v>98674</v>
       </c>
       <c r="I398" s="1" t="s">
-        <v>249</v>
+        <v>260</v>
       </c>
     </row>
     <row r="399" spans="1:9" x14ac:dyDescent="0.35">
@@ -14132,24 +14135,24 @@
         <v>98674</v>
       </c>
       <c r="I399" s="1" t="s">
-        <v>17</v>
+        <v>249</v>
       </c>
     </row>
     <row r="400" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A400" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="B400" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C400" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D400" t="s">
+        <v>11</v>
+      </c>
+      <c r="E400" t="s">
         <v>593</v>
-      </c>
-      <c r="B400" s="3" t="s">
-        <v>594</v>
-      </c>
-      <c r="C400" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D400" t="s">
-        <v>8</v>
-      </c>
-      <c r="E400" t="s">
-        <v>595</v>
       </c>
       <c r="F400" t="s">
         <v>243</v>
@@ -14161,24 +14164,24 @@
         <v>98674</v>
       </c>
       <c r="I400" s="1" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
     </row>
     <row r="401" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A401" s="3" t="s">
-        <v>153</v>
+        <v>594</v>
       </c>
       <c r="B401" s="3" t="s">
-        <v>238</v>
+        <v>595</v>
       </c>
       <c r="C401" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D401" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="E401" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="F401" t="s">
         <v>243</v>
@@ -14198,19 +14201,19 @@
         <v>153</v>
       </c>
       <c r="B402" s="3" t="s">
-        <v>25</v>
+        <v>238</v>
       </c>
       <c r="C402" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D402" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="E402" t="s">
         <v>596</v>
       </c>
       <c r="F402" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="G402" t="s">
         <v>11</v>
@@ -14219,15 +14222,15 @@
         <v>98674</v>
       </c>
       <c r="I402" s="1" t="s">
-        <v>260</v>
+        <v>12</v>
       </c>
     </row>
     <row r="403" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A403" s="3" t="s">
-        <v>393</v>
+        <v>153</v>
       </c>
       <c r="B403" s="3" t="s">
-        <v>189</v>
+        <v>25</v>
       </c>
       <c r="C403" s="1" t="s">
         <v>7</v>
@@ -14239,7 +14242,7 @@
         <v>597</v>
       </c>
       <c r="F403" t="s">
-        <v>27</v>
+        <v>240</v>
       </c>
       <c r="G403" t="s">
         <v>11</v>
@@ -14282,10 +14285,10 @@
     </row>
     <row r="405" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A405" s="3" t="s">
-        <v>167</v>
+        <v>393</v>
       </c>
       <c r="B405" s="3" t="s">
-        <v>168</v>
+        <v>189</v>
       </c>
       <c r="C405" s="1" t="s">
         <v>7</v>
@@ -14297,7 +14300,7 @@
         <v>599</v>
       </c>
       <c r="F405" t="s">
-        <v>236</v>
+        <v>27</v>
       </c>
       <c r="G405" t="s">
         <v>11</v>
@@ -14306,15 +14309,15 @@
         <v>98674</v>
       </c>
       <c r="I405" s="1" t="s">
-        <v>20</v>
+        <v>260</v>
       </c>
     </row>
     <row r="406" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A406" s="3" t="s">
-        <v>153</v>
+        <v>167</v>
       </c>
       <c r="B406" s="3" t="s">
-        <v>25</v>
+        <v>168</v>
       </c>
       <c r="C406" s="1" t="s">
         <v>7</v>
@@ -14326,7 +14329,7 @@
         <v>600</v>
       </c>
       <c r="F406" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="G406" t="s">
         <v>11</v>
@@ -14335,25 +14338,25 @@
         <v>98674</v>
       </c>
       <c r="I406" s="1" t="s">
-        <v>249</v>
+        <v>20</v>
       </c>
     </row>
     <row r="407" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A407" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="B407" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C407" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D407" t="s">
+        <v>11</v>
+      </c>
+      <c r="E407" t="s">
         <v>601</v>
       </c>
-      <c r="B407" s="3" t="s">
-        <v>602</v>
-      </c>
-      <c r="C407" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D407" t="s">
-        <v>8</v>
-      </c>
-      <c r="E407" t="s">
-        <v>603</v>
-      </c>
       <c r="F407" t="s">
         <v>240</v>
       </c>
@@ -14364,21 +14367,21 @@
         <v>98674</v>
       </c>
       <c r="I407" s="1" t="s">
-        <v>12</v>
+        <v>249</v>
       </c>
     </row>
     <row r="408" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A408" s="3" t="s">
-        <v>153</v>
+        <v>602</v>
       </c>
       <c r="B408" s="3" t="s">
-        <v>14</v>
+        <v>603</v>
       </c>
       <c r="C408" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D408" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E408" t="s">
         <v>604</v>
@@ -14393,25 +14396,25 @@
         <v>98674</v>
       </c>
       <c r="I408" s="1" t="s">
-        <v>237</v>
+        <v>12</v>
       </c>
     </row>
     <row r="409" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A409" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="B409" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C409" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D409" t="s">
+        <v>11</v>
+      </c>
+      <c r="E409" t="s">
         <v>605</v>
       </c>
-      <c r="B409" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="C409" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D409" t="s">
-        <v>8</v>
-      </c>
-      <c r="E409" t="s">
-        <v>606</v>
-      </c>
       <c r="F409" t="s">
         <v>240</v>
       </c>
@@ -14422,27 +14425,27 @@
         <v>98674</v>
       </c>
       <c r="I409" s="1" t="s">
-        <v>12</v>
+        <v>237</v>
       </c>
     </row>
     <row r="410" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A410" s="3" t="s">
-        <v>24</v>
+        <v>606</v>
       </c>
       <c r="B410" s="3" t="s">
-        <v>14</v>
+        <v>144</v>
       </c>
       <c r="C410" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D410" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E410" t="s">
         <v>607</v>
       </c>
       <c r="F410" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="G410" t="s">
         <v>11</v>
@@ -14451,15 +14454,15 @@
         <v>98674</v>
       </c>
       <c r="I410" s="1" t="s">
-        <v>249</v>
+        <v>12</v>
       </c>
     </row>
     <row r="411" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A411" s="3" t="s">
-        <v>153</v>
+        <v>24</v>
       </c>
       <c r="B411" s="3" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="C411" s="1" t="s">
         <v>7</v>
@@ -14471,7 +14474,7 @@
         <v>608</v>
       </c>
       <c r="F411" t="s">
-        <v>270</v>
+        <v>243</v>
       </c>
       <c r="G411" t="s">
         <v>11</v>
@@ -14480,7 +14483,7 @@
         <v>98674</v>
       </c>
       <c r="I411" s="1" t="s">
-        <v>17</v>
+        <v>249</v>
       </c>
     </row>
     <row r="412" spans="1:9" x14ac:dyDescent="0.35">
@@ -14488,7 +14491,7 @@
         <v>153</v>
       </c>
       <c r="B412" s="3" t="s">
-        <v>241</v>
+        <v>25</v>
       </c>
       <c r="C412" s="1" t="s">
         <v>7</v>
@@ -14500,7 +14503,7 @@
         <v>609</v>
       </c>
       <c r="F412" t="s">
-        <v>11</v>
+        <v>270</v>
       </c>
       <c r="G412" t="s">
         <v>11</v>
@@ -14509,7 +14512,7 @@
         <v>98674</v>
       </c>
       <c r="I412" s="1" t="s">
-        <v>260</v>
+        <v>17</v>
       </c>
     </row>
     <row r="413" spans="1:9" x14ac:dyDescent="0.35">
@@ -14517,7 +14520,7 @@
         <v>153</v>
       </c>
       <c r="B413" s="3" t="s">
-        <v>25</v>
+        <v>241</v>
       </c>
       <c r="C413" s="1" t="s">
         <v>7</v>
@@ -14529,7 +14532,7 @@
         <v>610</v>
       </c>
       <c r="F413" t="s">
-        <v>240</v>
+        <v>11</v>
       </c>
       <c r="G413" t="s">
         <v>11</v>
@@ -14538,15 +14541,15 @@
         <v>98674</v>
       </c>
       <c r="I413" s="1" t="s">
-        <v>237</v>
+        <v>260</v>
       </c>
     </row>
     <row r="414" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A414" s="3" t="s">
-        <v>393</v>
+        <v>153</v>
       </c>
       <c r="B414" s="3" t="s">
-        <v>189</v>
+        <v>25</v>
       </c>
       <c r="C414" s="1" t="s">
         <v>7</v>
@@ -14558,7 +14561,7 @@
         <v>611</v>
       </c>
       <c r="F414" t="s">
-        <v>27</v>
+        <v>240</v>
       </c>
       <c r="G414" t="s">
         <v>11</v>
@@ -14567,15 +14570,15 @@
         <v>98674</v>
       </c>
       <c r="I414" s="1" t="s">
-        <v>260</v>
+        <v>237</v>
       </c>
     </row>
     <row r="415" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A415" s="3" t="s">
-        <v>153</v>
+        <v>393</v>
       </c>
       <c r="B415" s="3" t="s">
-        <v>14</v>
+        <v>189</v>
       </c>
       <c r="C415" s="1" t="s">
         <v>7</v>
@@ -14587,7 +14590,7 @@
         <v>612</v>
       </c>
       <c r="F415" t="s">
-        <v>240</v>
+        <v>27</v>
       </c>
       <c r="G415" t="s">
         <v>11</v>
@@ -14596,15 +14599,15 @@
         <v>98674</v>
       </c>
       <c r="I415" s="1" t="s">
-        <v>237</v>
+        <v>260</v>
       </c>
     </row>
     <row r="416" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A416" s="3" t="s">
-        <v>280</v>
+        <v>153</v>
       </c>
       <c r="B416" s="3" t="s">
-        <v>257</v>
+        <v>14</v>
       </c>
       <c r="C416" s="1" t="s">
         <v>7</v>
@@ -14616,7 +14619,7 @@
         <v>613</v>
       </c>
       <c r="F416" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="G416" t="s">
         <v>11</v>
@@ -14625,15 +14628,15 @@
         <v>98674</v>
       </c>
       <c r="I416" s="1" t="s">
-        <v>260</v>
+        <v>237</v>
       </c>
     </row>
     <row r="417" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A417" s="3" t="s">
-        <v>332</v>
+        <v>280</v>
       </c>
       <c r="B417" s="3" t="s">
-        <v>247</v>
+        <v>257</v>
       </c>
       <c r="C417" s="1" t="s">
         <v>7</v>
@@ -14642,7 +14645,7 @@
         <v>11</v>
       </c>
       <c r="E417" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="F417" t="s">
         <v>243</v>
@@ -14654,15 +14657,15 @@
         <v>98674</v>
       </c>
       <c r="I417" s="1" t="s">
-        <v>249</v>
+        <v>260</v>
       </c>
     </row>
     <row r="418" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A418" s="3" t="s">
-        <v>153</v>
+        <v>332</v>
       </c>
       <c r="B418" s="3" t="s">
-        <v>25</v>
+        <v>247</v>
       </c>
       <c r="C418" s="1" t="s">
         <v>7</v>
@@ -14683,7 +14686,7 @@
         <v>98674</v>
       </c>
       <c r="I418" s="1" t="s">
-        <v>260</v>
+        <v>249</v>
       </c>
     </row>
     <row r="419" spans="1:9" x14ac:dyDescent="0.35">
@@ -14691,7 +14694,7 @@
         <v>153</v>
       </c>
       <c r="B419" s="3" t="s">
-        <v>241</v>
+        <v>25</v>
       </c>
       <c r="C419" s="1" t="s">
         <v>7</v>
@@ -14712,7 +14715,7 @@
         <v>98674</v>
       </c>
       <c r="I419" s="1" t="s">
-        <v>273</v>
+        <v>260</v>
       </c>
     </row>
     <row r="420" spans="1:9" x14ac:dyDescent="0.35">
@@ -14720,7 +14723,7 @@
         <v>153</v>
       </c>
       <c r="B420" s="3" t="s">
-        <v>25</v>
+        <v>241</v>
       </c>
       <c r="C420" s="1" t="s">
         <v>7</v>
@@ -14741,15 +14744,15 @@
         <v>98674</v>
       </c>
       <c r="I420" s="1" t="s">
-        <v>249</v>
+        <v>273</v>
       </c>
     </row>
     <row r="421" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A421" s="3" t="s">
-        <v>280</v>
+        <v>153</v>
       </c>
       <c r="B421" s="3" t="s">
-        <v>241</v>
+        <v>25</v>
       </c>
       <c r="C421" s="1" t="s">
         <v>7</v>
@@ -14761,7 +14764,7 @@
         <v>617</v>
       </c>
       <c r="F421" t="s">
-        <v>270</v>
+        <v>243</v>
       </c>
       <c r="G421" t="s">
         <v>11</v>
@@ -14770,12 +14773,12 @@
         <v>98674</v>
       </c>
       <c r="I421" s="1" t="s">
-        <v>260</v>
+        <v>249</v>
       </c>
     </row>
     <row r="422" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A422" s="3" t="s">
-        <v>153</v>
+        <v>280</v>
       </c>
       <c r="B422" s="3" t="s">
         <v>241</v>
@@ -14790,7 +14793,7 @@
         <v>618</v>
       </c>
       <c r="F422" t="s">
-        <v>16</v>
+        <v>270</v>
       </c>
       <c r="G422" t="s">
         <v>11</v>
@@ -14799,15 +14802,15 @@
         <v>98674</v>
       </c>
       <c r="I422" s="1" t="s">
-        <v>17</v>
+        <v>260</v>
       </c>
     </row>
     <row r="423" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A423" s="3" t="s">
-        <v>462</v>
+        <v>153</v>
       </c>
       <c r="B423" s="3" t="s">
-        <v>14</v>
+        <v>241</v>
       </c>
       <c r="C423" s="1" t="s">
         <v>7</v>
@@ -14819,7 +14822,7 @@
         <v>619</v>
       </c>
       <c r="F423" t="s">
-        <v>240</v>
+        <v>16</v>
       </c>
       <c r="G423" t="s">
         <v>11</v>
@@ -14833,10 +14836,10 @@
     </row>
     <row r="424" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A424" s="3" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="B424" s="3" t="s">
-        <v>255</v>
+        <v>14</v>
       </c>
       <c r="C424" s="1" t="s">
         <v>7</v>
@@ -14857,24 +14860,24 @@
         <v>98674</v>
       </c>
       <c r="I424" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="425" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A425" s="3" t="s">
+        <v>460</v>
+      </c>
+      <c r="B425" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="C425" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D425" t="s">
+        <v>11</v>
+      </c>
+      <c r="E425" t="s">
         <v>621</v>
-      </c>
-      <c r="B425" s="3" t="s">
-        <v>621</v>
-      </c>
-      <c r="C425" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="D425" t="s">
-        <v>11</v>
-      </c>
-      <c r="E425" t="s">
-        <v>620</v>
       </c>
       <c r="F425" t="s">
         <v>240</v>
@@ -14891,22 +14894,22 @@
     </row>
     <row r="426" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A426" s="3" t="s">
-        <v>312</v>
+        <v>622</v>
       </c>
       <c r="B426" s="3" t="s">
-        <v>313</v>
+        <v>622</v>
       </c>
       <c r="C426" s="1" t="s">
-        <v>7</v>
+        <v>114</v>
       </c>
       <c r="D426" t="s">
         <v>11</v>
       </c>
       <c r="E426" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="F426" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="G426" t="s">
         <v>11</v>
@@ -14920,22 +14923,22 @@
     </row>
     <row r="427" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A427" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="B427" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="C427" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D427" t="s">
+        <v>11</v>
+      </c>
+      <c r="E427" t="s">
         <v>623</v>
       </c>
-      <c r="B427" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="C427" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D427" t="s">
-        <v>8</v>
-      </c>
-      <c r="E427" t="s">
-        <v>624</v>
-      </c>
       <c r="F427" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="G427" t="s">
         <v>11</v>
@@ -14944,15 +14947,15 @@
         <v>98674</v>
       </c>
       <c r="I427" s="1" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="428" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A428" s="3" t="s">
-        <v>202</v>
+        <v>624</v>
       </c>
       <c r="B428" s="3" t="s">
-        <v>159</v>
+        <v>228</v>
       </c>
       <c r="C428" s="1" t="s">
         <v>7</v>
@@ -14978,22 +14981,22 @@
     </row>
     <row r="429" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A429" s="3" t="s">
-        <v>24</v>
+        <v>202</v>
       </c>
       <c r="B429" s="3" t="s">
-        <v>35</v>
+        <v>159</v>
       </c>
       <c r="C429" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D429" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E429" t="s">
         <v>626</v>
       </c>
       <c r="F429" t="s">
-        <v>16</v>
+        <v>240</v>
       </c>
       <c r="G429" t="s">
         <v>11</v>
@@ -15002,12 +15005,12 @@
         <v>98674</v>
       </c>
       <c r="I429" s="1" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
     </row>
     <row r="430" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A430" s="3" t="s">
-        <v>280</v>
+        <v>24</v>
       </c>
       <c r="B430" s="3" t="s">
         <v>35</v>
@@ -15022,7 +15025,7 @@
         <v>627</v>
       </c>
       <c r="F430" t="s">
-        <v>240</v>
+        <v>16</v>
       </c>
       <c r="G430" t="s">
         <v>11</v>
@@ -15031,25 +15034,25 @@
         <v>98674</v>
       </c>
       <c r="I430" s="1" t="s">
-        <v>249</v>
+        <v>20</v>
       </c>
     </row>
     <row r="431" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A431" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="B431" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C431" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D431" t="s">
+        <v>11</v>
+      </c>
+      <c r="E431" t="s">
         <v>628</v>
       </c>
-      <c r="B431" s="3" t="s">
-        <v>506</v>
-      </c>
-      <c r="C431" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D431" t="s">
-        <v>11</v>
-      </c>
-      <c r="E431" t="s">
-        <v>627</v>
-      </c>
       <c r="F431" t="s">
         <v>240</v>
       </c>
@@ -15060,12 +15063,12 @@
         <v>98674</v>
       </c>
       <c r="I431" s="1" t="s">
-        <v>237</v>
+        <v>249</v>
       </c>
     </row>
     <row r="432" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A432" s="3" t="s">
-        <v>153</v>
+        <v>629</v>
       </c>
       <c r="B432" s="3" t="s">
         <v>506</v>
@@ -15077,7 +15080,7 @@
         <v>11</v>
       </c>
       <c r="E432" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="F432" t="s">
         <v>240</v>
@@ -15089,7 +15092,7 @@
         <v>98674</v>
       </c>
       <c r="I432" s="1" t="s">
-        <v>249</v>
+        <v>237</v>
       </c>
     </row>
     <row r="433" spans="1:9" x14ac:dyDescent="0.35">
@@ -15097,7 +15100,7 @@
         <v>153</v>
       </c>
       <c r="B433" s="3" t="s">
-        <v>37</v>
+        <v>506</v>
       </c>
       <c r="C433" s="1" t="s">
         <v>7</v>
@@ -15118,27 +15121,27 @@
         <v>98674</v>
       </c>
       <c r="I433" s="1" t="s">
-        <v>260</v>
+        <v>249</v>
       </c>
     </row>
     <row r="434" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A434" s="3" t="s">
-        <v>254</v>
+        <v>153</v>
       </c>
       <c r="B434" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C434" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D434" t="s">
+        <v>11</v>
+      </c>
+      <c r="E434" t="s">
         <v>631</v>
       </c>
-      <c r="C434" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D434" t="s">
-        <v>11</v>
-      </c>
-      <c r="E434" t="s">
-        <v>632</v>
-      </c>
       <c r="F434" t="s">
-        <v>16</v>
+        <v>240</v>
       </c>
       <c r="G434" t="s">
         <v>11</v>
@@ -15147,15 +15150,15 @@
         <v>98674</v>
       </c>
       <c r="I434" s="1" t="s">
-        <v>249</v>
+        <v>260</v>
       </c>
     </row>
     <row r="435" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A435" s="3" t="s">
-        <v>343</v>
+        <v>254</v>
       </c>
       <c r="B435" s="3" t="s">
-        <v>244</v>
+        <v>632</v>
       </c>
       <c r="C435" s="1" t="s">
         <v>7</v>
@@ -15167,7 +15170,7 @@
         <v>633</v>
       </c>
       <c r="F435" t="s">
-        <v>240</v>
+        <v>16</v>
       </c>
       <c r="G435" t="s">
         <v>11</v>
@@ -15176,27 +15179,27 @@
         <v>98674</v>
       </c>
       <c r="I435" s="1" t="s">
-        <v>84</v>
+        <v>249</v>
       </c>
     </row>
     <row r="436" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A436" s="3" t="s">
-        <v>202</v>
+        <v>343</v>
       </c>
       <c r="B436" s="3" t="s">
-        <v>356</v>
+        <v>244</v>
       </c>
       <c r="C436" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D436" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="E436" t="s">
         <v>634</v>
       </c>
       <c r="F436" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="G436" t="s">
         <v>11</v>
@@ -15205,27 +15208,27 @@
         <v>98674</v>
       </c>
       <c r="I436" s="1" t="s">
-        <v>46</v>
+        <v>84</v>
       </c>
     </row>
     <row r="437" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A437" s="3" t="s">
-        <v>280</v>
+        <v>202</v>
       </c>
       <c r="B437" s="3" t="s">
-        <v>30</v>
+        <v>356</v>
       </c>
       <c r="C437" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D437" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="E437" t="s">
         <v>635</v>
       </c>
       <c r="F437" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="G437" t="s">
         <v>11</v>
@@ -15234,15 +15237,15 @@
         <v>98674</v>
       </c>
       <c r="I437" s="1" t="s">
-        <v>260</v>
+        <v>46</v>
       </c>
     </row>
     <row r="438" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A438" s="3" t="s">
-        <v>153</v>
+        <v>280</v>
       </c>
       <c r="B438" s="3" t="s">
-        <v>241</v>
+        <v>30</v>
       </c>
       <c r="C438" s="1" t="s">
         <v>7</v>
@@ -15254,7 +15257,7 @@
         <v>636</v>
       </c>
       <c r="F438" t="s">
-        <v>10</v>
+        <v>240</v>
       </c>
       <c r="G438" t="s">
         <v>11</v>
@@ -15268,10 +15271,10 @@
     </row>
     <row r="439" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A439" s="3" t="s">
-        <v>449</v>
+        <v>153</v>
       </c>
       <c r="B439" s="3" t="s">
-        <v>257</v>
+        <v>241</v>
       </c>
       <c r="C439" s="1" t="s">
         <v>7</v>
@@ -15283,7 +15286,7 @@
         <v>637</v>
       </c>
       <c r="F439" t="s">
-        <v>236</v>
+        <v>10</v>
       </c>
       <c r="G439" t="s">
         <v>11</v>
@@ -15292,27 +15295,27 @@
         <v>98674</v>
       </c>
       <c r="I439" s="1" t="s">
-        <v>20</v>
+        <v>260</v>
       </c>
     </row>
     <row r="440" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A440" s="3" t="s">
-        <v>153</v>
+        <v>449</v>
       </c>
       <c r="B440" s="3" t="s">
-        <v>24</v>
+        <v>257</v>
       </c>
       <c r="C440" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D440" t="s">
-        <v>320</v>
+        <v>11</v>
       </c>
       <c r="E440" t="s">
         <v>638</v>
       </c>
       <c r="F440" t="s">
-        <v>10</v>
+        <v>236</v>
       </c>
       <c r="G440" t="s">
         <v>11</v>
@@ -15326,10 +15329,10 @@
     </row>
     <row r="441" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A441" s="3" t="s">
-        <v>639</v>
+        <v>153</v>
       </c>
       <c r="B441" s="3" t="s">
-        <v>640</v>
+        <v>24</v>
       </c>
       <c r="C441" s="1" t="s">
         <v>7</v>
@@ -15338,7 +15341,7 @@
         <v>320</v>
       </c>
       <c r="E441" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="F441" t="s">
         <v>10</v>
@@ -15350,12 +15353,12 @@
         <v>98674</v>
       </c>
       <c r="I441" s="1" t="s">
-        <v>260</v>
+        <v>20</v>
       </c>
     </row>
     <row r="442" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A442" s="3" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="B442" s="3" t="s">
         <v>641</v>
@@ -15367,7 +15370,7 @@
         <v>320</v>
       </c>
       <c r="E442" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="F442" t="s">
         <v>10</v>
@@ -15379,7 +15382,7 @@
         <v>98674</v>
       </c>
       <c r="I442" s="1" t="s">
-        <v>20</v>
+        <v>260</v>
       </c>
     </row>
     <row r="443" spans="1:9" x14ac:dyDescent="0.35">
@@ -15396,7 +15399,7 @@
         <v>320</v>
       </c>
       <c r="E443" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="F443" t="s">
         <v>10</v>
@@ -15408,12 +15411,12 @@
         <v>98674</v>
       </c>
       <c r="I443" s="1" t="s">
-        <v>260</v>
+        <v>20</v>
       </c>
     </row>
     <row r="444" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A444" s="3" t="s">
-        <v>432</v>
+        <v>643</v>
       </c>
       <c r="B444" s="3" t="s">
         <v>643</v>
@@ -15425,7 +15428,7 @@
         <v>320</v>
       </c>
       <c r="E444" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="F444" t="s">
         <v>10</v>
@@ -15437,15 +15440,15 @@
         <v>98674</v>
       </c>
       <c r="I444" s="1" t="s">
-        <v>20</v>
+        <v>260</v>
       </c>
     </row>
     <row r="445" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A445" s="3" t="s">
+        <v>432</v>
+      </c>
+      <c r="B445" s="3" t="s">
         <v>644</v>
-      </c>
-      <c r="B445" s="3" t="s">
-        <v>25</v>
       </c>
       <c r="C445" s="1" t="s">
         <v>7</v>
@@ -15454,7 +15457,7 @@
         <v>320</v>
       </c>
       <c r="E445" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="F445" t="s">
         <v>10</v>
@@ -15466,15 +15469,15 @@
         <v>98674</v>
       </c>
       <c r="I445" s="1" t="s">
-        <v>260</v>
+        <v>20</v>
       </c>
     </row>
     <row r="446" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A446" s="3" t="s">
-        <v>28</v>
+        <v>645</v>
       </c>
       <c r="B446" s="3" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="C446" s="1" t="s">
         <v>7</v>
@@ -15483,7 +15486,7 @@
         <v>320</v>
       </c>
       <c r="E446" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="F446" t="s">
         <v>10</v>
@@ -15495,24 +15498,24 @@
         <v>98674</v>
       </c>
       <c r="I446" s="1" t="s">
-        <v>20</v>
+        <v>260</v>
       </c>
     </row>
     <row r="447" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A447" s="3" t="s">
-        <v>349</v>
+        <v>28</v>
       </c>
       <c r="B447" s="3" t="s">
-        <v>401</v>
+        <v>14</v>
       </c>
       <c r="C447" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D447" t="s">
-        <v>645</v>
+        <v>320</v>
       </c>
       <c r="E447" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="F447" t="s">
         <v>10</v>
@@ -15529,19 +15532,19 @@
     </row>
     <row r="448" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A448" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="B448" s="3" t="s">
+        <v>401</v>
+      </c>
+      <c r="C448" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D448" t="s">
         <v>646</v>
       </c>
-      <c r="B448" s="3" t="s">
-        <v>647</v>
-      </c>
-      <c r="C448" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D448" t="s">
-        <v>645</v>
-      </c>
       <c r="E448" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="F448" t="s">
         <v>10</v>
@@ -15558,22 +15561,22 @@
     </row>
     <row r="449" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A449" s="3" t="s">
-        <v>153</v>
+        <v>647</v>
       </c>
       <c r="B449" s="3" t="s">
-        <v>35</v>
+        <v>648</v>
       </c>
       <c r="C449" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D449" t="s">
-        <v>11</v>
+        <v>646</v>
       </c>
       <c r="E449" t="s">
-        <v>648</v>
+        <v>639</v>
       </c>
       <c r="F449" t="s">
-        <v>240</v>
+        <v>10</v>
       </c>
       <c r="G449" t="s">
         <v>11</v>
@@ -15587,10 +15590,10 @@
     </row>
     <row r="450" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A450" s="3" t="s">
-        <v>28</v>
+        <v>153</v>
       </c>
       <c r="B450" s="3" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="C450" s="1" t="s">
         <v>7</v>
@@ -15611,24 +15614,24 @@
         <v>98674</v>
       </c>
       <c r="I450" s="1" t="s">
-        <v>260</v>
+        <v>20</v>
       </c>
     </row>
     <row r="451" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A451" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B451" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C451" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D451" t="s">
+        <v>11</v>
+      </c>
+      <c r="E451" t="s">
         <v>650</v>
-      </c>
-      <c r="B451" s="3" t="s">
-        <v>651</v>
-      </c>
-      <c r="C451" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D451" t="s">
-        <v>11</v>
-      </c>
-      <c r="E451" t="s">
-        <v>649</v>
       </c>
       <c r="F451" t="s">
         <v>240</v>
@@ -15645,7 +15648,7 @@
     </row>
     <row r="452" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A452" s="3" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="B452" s="3" t="s">
         <v>652</v>
@@ -15657,7 +15660,7 @@
         <v>11</v>
       </c>
       <c r="E452" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="F452" t="s">
         <v>240</v>
@@ -15674,10 +15677,10 @@
     </row>
     <row r="453" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A453" s="3" t="s">
-        <v>153</v>
+        <v>653</v>
       </c>
       <c r="B453" s="3" t="s">
-        <v>241</v>
+        <v>653</v>
       </c>
       <c r="C453" s="1" t="s">
         <v>7</v>
@@ -15686,10 +15689,10 @@
         <v>11</v>
       </c>
       <c r="E453" t="s">
-        <v>653</v>
+        <v>650</v>
       </c>
       <c r="F453" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="G453" t="s">
         <v>11</v>
@@ -15698,7 +15701,7 @@
         <v>98674</v>
       </c>
       <c r="I453" s="1" t="s">
-        <v>237</v>
+        <v>260</v>
       </c>
     </row>
     <row r="454" spans="1:9" x14ac:dyDescent="0.35">
@@ -15706,7 +15709,7 @@
         <v>153</v>
       </c>
       <c r="B454" s="3" t="s">
-        <v>35</v>
+        <v>241</v>
       </c>
       <c r="C454" s="1" t="s">
         <v>7</v>
@@ -15718,7 +15721,7 @@
         <v>654</v>
       </c>
       <c r="F454" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="G454" t="s">
         <v>11</v>
@@ -15735,7 +15738,7 @@
         <v>153</v>
       </c>
       <c r="B455" s="3" t="s">
-        <v>241</v>
+        <v>35</v>
       </c>
       <c r="C455" s="1" t="s">
         <v>7</v>
@@ -15756,25 +15759,25 @@
         <v>98674</v>
       </c>
       <c r="I455" s="1" t="s">
-        <v>260</v>
+        <v>237</v>
       </c>
     </row>
     <row r="456" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A456" s="3" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="B456" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="C456" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D456" t="s">
+        <v>11</v>
+      </c>
+      <c r="E456" t="s">
         <v>656</v>
       </c>
-      <c r="C456" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D456" t="s">
-        <v>23</v>
-      </c>
-      <c r="E456" t="s">
-        <v>657</v>
-      </c>
       <c r="F456" t="s">
         <v>240</v>
       </c>
@@ -15785,27 +15788,27 @@
         <v>98674</v>
       </c>
       <c r="I456" s="1" t="s">
-        <v>46</v>
+        <v>260</v>
       </c>
     </row>
     <row r="457" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A457" s="3" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="B457" s="3" t="s">
-        <v>241</v>
+        <v>657</v>
       </c>
       <c r="C457" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D457" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="E457" t="s">
         <v>658</v>
       </c>
       <c r="F457" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="G457" t="s">
         <v>11</v>
@@ -15814,7 +15817,7 @@
         <v>98674</v>
       </c>
       <c r="I457" s="1" t="s">
-        <v>237</v>
+        <v>46</v>
       </c>
     </row>
     <row r="458" spans="1:9" x14ac:dyDescent="0.35">
@@ -15834,7 +15837,7 @@
         <v>659</v>
       </c>
       <c r="F458" t="s">
-        <v>270</v>
+        <v>243</v>
       </c>
       <c r="G458" t="s">
         <v>11</v>
@@ -15851,7 +15854,7 @@
         <v>153</v>
       </c>
       <c r="B459" s="3" t="s">
-        <v>25</v>
+        <v>241</v>
       </c>
       <c r="C459" s="1" t="s">
         <v>7</v>
@@ -15863,7 +15866,7 @@
         <v>660</v>
       </c>
       <c r="F459" t="s">
-        <v>243</v>
+        <v>270</v>
       </c>
       <c r="G459" t="s">
         <v>11</v>
@@ -15872,7 +15875,7 @@
         <v>98674</v>
       </c>
       <c r="I459" s="1" t="s">
-        <v>273</v>
+        <v>237</v>
       </c>
     </row>
     <row r="460" spans="1:9" x14ac:dyDescent="0.35">
@@ -15906,10 +15909,10 @@
     </row>
     <row r="461" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A461" s="3" t="s">
-        <v>280</v>
+        <v>153</v>
       </c>
       <c r="B461" s="3" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="C461" s="1" t="s">
         <v>7</v>
@@ -15921,7 +15924,7 @@
         <v>662</v>
       </c>
       <c r="F461" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="G461" t="s">
         <v>11</v>
@@ -15930,15 +15933,15 @@
         <v>98674</v>
       </c>
       <c r="I461" s="1" t="s">
-        <v>260</v>
+        <v>273</v>
       </c>
     </row>
     <row r="462" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A462" s="3" t="s">
-        <v>153</v>
+        <v>280</v>
       </c>
       <c r="B462" s="3" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="C462" s="1" t="s">
         <v>7</v>
@@ -15950,7 +15953,7 @@
         <v>663</v>
       </c>
       <c r="F462" t="s">
-        <v>270</v>
+        <v>240</v>
       </c>
       <c r="G462" t="s">
         <v>11</v>
@@ -15959,15 +15962,15 @@
         <v>98674</v>
       </c>
       <c r="I462" s="1" t="s">
-        <v>249</v>
+        <v>260</v>
       </c>
     </row>
     <row r="463" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A463" s="3" t="s">
-        <v>24</v>
+        <v>153</v>
       </c>
       <c r="B463" s="3" t="s">
-        <v>189</v>
+        <v>25</v>
       </c>
       <c r="C463" s="1" t="s">
         <v>7</v>
@@ -15979,7 +15982,7 @@
         <v>664</v>
       </c>
       <c r="F463" t="s">
-        <v>16</v>
+        <v>270</v>
       </c>
       <c r="G463" t="s">
         <v>11</v>
@@ -15988,15 +15991,15 @@
         <v>98674</v>
       </c>
       <c r="I463" s="1" t="s">
-        <v>260</v>
+        <v>249</v>
       </c>
     </row>
     <row r="464" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A464" s="3" t="s">
-        <v>332</v>
+        <v>24</v>
       </c>
       <c r="B464" s="3" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="C464" s="1" t="s">
         <v>7</v>
@@ -16008,7 +16011,7 @@
         <v>665</v>
       </c>
       <c r="F464" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="G464" t="s">
         <v>11</v>
@@ -16017,27 +16020,27 @@
         <v>98674</v>
       </c>
       <c r="I464" s="1" t="s">
-        <v>249</v>
+        <v>260</v>
       </c>
     </row>
     <row r="465" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A465" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="B465" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="C465" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D465" t="s">
+        <v>11</v>
+      </c>
+      <c r="E465" t="s">
         <v>666</v>
       </c>
-      <c r="B465" s="3" t="s">
-        <v>667</v>
-      </c>
-      <c r="C465" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D465" t="s">
-        <v>8</v>
-      </c>
-      <c r="E465" t="s">
-        <v>668</v>
-      </c>
       <c r="F465" t="s">
-        <v>240</v>
+        <v>10</v>
       </c>
       <c r="G465" t="s">
         <v>11</v>
@@ -16046,27 +16049,27 @@
         <v>98674</v>
       </c>
       <c r="I465" s="1" t="s">
-        <v>12</v>
+        <v>249</v>
       </c>
     </row>
     <row r="466" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A466" s="3" t="s">
-        <v>153</v>
+        <v>667</v>
       </c>
       <c r="B466" s="3" t="s">
-        <v>14</v>
+        <v>668</v>
       </c>
       <c r="C466" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D466" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E466" t="s">
         <v>669</v>
       </c>
       <c r="F466" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="G466" t="s">
         <v>11</v>
@@ -16075,12 +16078,12 @@
         <v>98674</v>
       </c>
       <c r="I466" s="1" t="s">
-        <v>237</v>
+        <v>12</v>
       </c>
     </row>
     <row r="467" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A467" s="3" t="s">
-        <v>28</v>
+        <v>153</v>
       </c>
       <c r="B467" s="3" t="s">
         <v>14</v>
@@ -16089,7 +16092,7 @@
         <v>7</v>
       </c>
       <c r="D467" t="s">
-        <v>306</v>
+        <v>11</v>
       </c>
       <c r="E467" t="s">
         <v>670</v>
@@ -16104,21 +16107,21 @@
         <v>98674</v>
       </c>
       <c r="I467" s="1" t="s">
-        <v>17</v>
+        <v>237</v>
       </c>
     </row>
     <row r="468" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A468" s="3" t="s">
-        <v>332</v>
+        <v>28</v>
       </c>
       <c r="B468" s="3" t="s">
-        <v>255</v>
+        <v>14</v>
       </c>
       <c r="C468" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D468" t="s">
-        <v>11</v>
+        <v>306</v>
       </c>
       <c r="E468" t="s">
         <v>671</v>
@@ -16133,15 +16136,15 @@
         <v>98674</v>
       </c>
       <c r="I468" s="1" t="s">
-        <v>249</v>
+        <v>17</v>
       </c>
     </row>
     <row r="469" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A469" s="3" t="s">
-        <v>153</v>
+        <v>332</v>
       </c>
       <c r="B469" s="3" t="s">
-        <v>244</v>
+        <v>255</v>
       </c>
       <c r="C469" s="1" t="s">
         <v>7</v>
@@ -16156,13 +16159,13 @@
         <v>243</v>
       </c>
       <c r="G469" t="s">
-        <v>306</v>
+        <v>11</v>
       </c>
       <c r="H469">
         <v>98674</v>
       </c>
       <c r="I469" s="1" t="s">
-        <v>237</v>
+        <v>249</v>
       </c>
     </row>
     <row r="470" spans="1:9" x14ac:dyDescent="0.35">
@@ -16170,7 +16173,7 @@
         <v>153</v>
       </c>
       <c r="B470" s="3" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="C470" s="1" t="s">
         <v>7</v>
@@ -16182,16 +16185,16 @@
         <v>673</v>
       </c>
       <c r="F470" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="G470" t="s">
-        <v>11</v>
+        <v>306</v>
       </c>
       <c r="H470">
         <v>98674</v>
       </c>
       <c r="I470" s="1" t="s">
-        <v>20</v>
+        <v>237</v>
       </c>
     </row>
     <row r="471" spans="1:9" x14ac:dyDescent="0.35">
@@ -16199,7 +16202,7 @@
         <v>153</v>
       </c>
       <c r="B471" s="3" t="s">
-        <v>25</v>
+        <v>241</v>
       </c>
       <c r="C471" s="1" t="s">
         <v>7</v>
@@ -16220,7 +16223,7 @@
         <v>98674</v>
       </c>
       <c r="I471" s="1" t="s">
-        <v>249</v>
+        <v>20</v>
       </c>
     </row>
     <row r="472" spans="1:9" x14ac:dyDescent="0.35">
@@ -16228,7 +16231,7 @@
         <v>153</v>
       </c>
       <c r="B472" s="3" t="s">
-        <v>241</v>
+        <v>25</v>
       </c>
       <c r="C472" s="1" t="s">
         <v>7</v>
@@ -16240,7 +16243,7 @@
         <v>675</v>
       </c>
       <c r="F472" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="G472" t="s">
         <v>11</v>
@@ -16249,7 +16252,7 @@
         <v>98674</v>
       </c>
       <c r="I472" s="1" t="s">
-        <v>260</v>
+        <v>249</v>
       </c>
     </row>
     <row r="473" spans="1:9" x14ac:dyDescent="0.35">
@@ -16257,7 +16260,7 @@
         <v>153</v>
       </c>
       <c r="B473" s="3" t="s">
-        <v>35</v>
+        <v>241</v>
       </c>
       <c r="C473" s="1" t="s">
         <v>7</v>
@@ -16269,7 +16272,7 @@
         <v>676</v>
       </c>
       <c r="F473" t="s">
-        <v>16</v>
+        <v>243</v>
       </c>
       <c r="G473" t="s">
         <v>11</v>
@@ -16283,7 +16286,7 @@
     </row>
     <row r="474" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A474" s="3" t="s">
-        <v>24</v>
+        <v>153</v>
       </c>
       <c r="B474" s="3" t="s">
         <v>35</v>
@@ -16298,7 +16301,7 @@
         <v>677</v>
       </c>
       <c r="F474" t="s">
-        <v>240</v>
+        <v>16</v>
       </c>
       <c r="G474" t="s">
         <v>11</v>
@@ -16307,27 +16310,27 @@
         <v>98674</v>
       </c>
       <c r="I474" s="1" t="s">
-        <v>237</v>
+        <v>260</v>
       </c>
     </row>
     <row r="475" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A475" s="3" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B475" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C475" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D475" t="s">
+        <v>11</v>
+      </c>
+      <c r="E475" t="s">
         <v>678</v>
       </c>
-      <c r="C475" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D475" t="s">
-        <v>11</v>
-      </c>
-      <c r="E475" t="s">
-        <v>679</v>
-      </c>
       <c r="F475" t="s">
-        <v>27</v>
+        <v>240</v>
       </c>
       <c r="G475" t="s">
         <v>11</v>
@@ -16336,15 +16339,15 @@
         <v>98674</v>
       </c>
       <c r="I475" s="1" t="s">
-        <v>260</v>
+        <v>237</v>
       </c>
     </row>
     <row r="476" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A476" s="3" t="s">
-        <v>280</v>
+        <v>28</v>
       </c>
       <c r="B476" s="3" t="s">
-        <v>241</v>
+        <v>679</v>
       </c>
       <c r="C476" s="1" t="s">
         <v>7</v>
@@ -16356,7 +16359,7 @@
         <v>680</v>
       </c>
       <c r="F476" t="s">
-        <v>240</v>
+        <v>27</v>
       </c>
       <c r="G476" t="s">
         <v>11</v>
@@ -16365,25 +16368,25 @@
         <v>98674</v>
       </c>
       <c r="I476" s="1" t="s">
-        <v>249</v>
+        <v>260</v>
       </c>
     </row>
     <row r="477" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A477" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="B477" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="C477" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D477" t="s">
+        <v>11</v>
+      </c>
+      <c r="E477" t="s">
         <v>681</v>
       </c>
-      <c r="B477" s="3" t="s">
-        <v>381</v>
-      </c>
-      <c r="C477" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D477" t="s">
-        <v>23</v>
-      </c>
-      <c r="E477" t="s">
-        <v>682</v>
-      </c>
       <c r="F477" t="s">
         <v>240</v>
       </c>
@@ -16394,27 +16397,27 @@
         <v>98674</v>
       </c>
       <c r="I477" s="1" t="s">
-        <v>46</v>
+        <v>249</v>
       </c>
     </row>
     <row r="478" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A478" s="3" t="s">
-        <v>153</v>
+        <v>682</v>
       </c>
       <c r="B478" s="3" t="s">
-        <v>241</v>
+        <v>381</v>
       </c>
       <c r="C478" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D478" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="E478" t="s">
         <v>683</v>
       </c>
       <c r="F478" t="s">
-        <v>295</v>
+        <v>240</v>
       </c>
       <c r="G478" t="s">
         <v>11</v>
@@ -16423,7 +16426,7 @@
         <v>98674</v>
       </c>
       <c r="I478" s="1" t="s">
-        <v>273</v>
+        <v>46</v>
       </c>
     </row>
     <row r="479" spans="1:9" x14ac:dyDescent="0.35">
@@ -16443,7 +16446,7 @@
         <v>684</v>
       </c>
       <c r="F479" t="s">
-        <v>240</v>
+        <v>295</v>
       </c>
       <c r="G479" t="s">
         <v>11</v>
@@ -16452,7 +16455,7 @@
         <v>98674</v>
       </c>
       <c r="I479" s="1" t="s">
-        <v>260</v>
+        <v>273</v>
       </c>
     </row>
     <row r="480" spans="1:9" x14ac:dyDescent="0.35">
@@ -16472,7 +16475,7 @@
         <v>685</v>
       </c>
       <c r="F480" t="s">
-        <v>16</v>
+        <v>240</v>
       </c>
       <c r="G480" t="s">
         <v>11</v>
@@ -16481,15 +16484,15 @@
         <v>98674</v>
       </c>
       <c r="I480" s="1" t="s">
-        <v>17</v>
+        <v>260</v>
       </c>
     </row>
     <row r="481" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A481" s="3" t="s">
-        <v>24</v>
+        <v>153</v>
       </c>
       <c r="B481" s="3" t="s">
-        <v>25</v>
+        <v>241</v>
       </c>
       <c r="C481" s="1" t="s">
         <v>7</v>
@@ -16501,7 +16504,7 @@
         <v>686</v>
       </c>
       <c r="F481" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="G481" t="s">
         <v>11</v>
@@ -16515,10 +16518,10 @@
     </row>
     <row r="482" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A482" s="3" t="s">
-        <v>153</v>
+        <v>24</v>
       </c>
       <c r="B482" s="3" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="C482" s="1" t="s">
         <v>7</v>
@@ -16530,7 +16533,7 @@
         <v>687</v>
       </c>
       <c r="F482" t="s">
-        <v>270</v>
+        <v>27</v>
       </c>
       <c r="G482" t="s">
         <v>11</v>
@@ -16547,7 +16550,7 @@
         <v>153</v>
       </c>
       <c r="B483" s="3" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="C483" s="1" t="s">
         <v>7</v>
@@ -16559,10 +16562,10 @@
         <v>688</v>
       </c>
       <c r="F483" t="s">
-        <v>243</v>
+        <v>270</v>
       </c>
       <c r="G483" t="s">
-        <v>306</v>
+        <v>11</v>
       </c>
       <c r="H483">
         <v>98674</v>
@@ -16576,7 +16579,7 @@
         <v>153</v>
       </c>
       <c r="B484" s="3" t="s">
-        <v>241</v>
+        <v>14</v>
       </c>
       <c r="C484" s="1" t="s">
         <v>7</v>
@@ -16591,21 +16594,21 @@
         <v>243</v>
       </c>
       <c r="G484" t="s">
-        <v>11</v>
+        <v>306</v>
       </c>
       <c r="H484">
         <v>98674</v>
       </c>
       <c r="I484" s="1" t="s">
-        <v>260</v>
+        <v>17</v>
       </c>
     </row>
     <row r="485" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A485" s="3" t="s">
-        <v>24</v>
+        <v>153</v>
       </c>
       <c r="B485" s="3" t="s">
-        <v>25</v>
+        <v>241</v>
       </c>
       <c r="C485" s="1" t="s">
         <v>7</v>
@@ -16617,7 +16620,7 @@
         <v>690</v>
       </c>
       <c r="F485" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="G485" t="s">
         <v>11</v>
@@ -16626,12 +16629,12 @@
         <v>98674</v>
       </c>
       <c r="I485" s="1" t="s">
-        <v>249</v>
+        <v>260</v>
       </c>
     </row>
     <row r="486" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A486" s="3" t="s">
-        <v>153</v>
+        <v>24</v>
       </c>
       <c r="B486" s="3" t="s">
         <v>25</v>
@@ -16646,7 +16649,7 @@
         <v>691</v>
       </c>
       <c r="F486" t="s">
-        <v>10</v>
+        <v>236</v>
       </c>
       <c r="G486" t="s">
         <v>11</v>
@@ -16655,27 +16658,27 @@
         <v>98674</v>
       </c>
       <c r="I486" s="1" t="s">
-        <v>260</v>
+        <v>249</v>
       </c>
     </row>
     <row r="487" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A487" s="3" t="s">
-        <v>393</v>
+        <v>153</v>
       </c>
       <c r="B487" s="3" t="s">
-        <v>156</v>
+        <v>25</v>
       </c>
       <c r="C487" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D487" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="E487" t="s">
         <v>692</v>
       </c>
       <c r="F487" t="s">
-        <v>243</v>
+        <v>10</v>
       </c>
       <c r="G487" t="s">
         <v>11</v>
@@ -16684,21 +16687,21 @@
         <v>98674</v>
       </c>
       <c r="I487" s="1" t="s">
-        <v>46</v>
+        <v>260</v>
       </c>
     </row>
     <row r="488" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A488" s="3" t="s">
-        <v>153</v>
+        <v>393</v>
       </c>
       <c r="B488" s="3" t="s">
-        <v>35</v>
+        <v>156</v>
       </c>
       <c r="C488" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D488" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="E488" t="s">
         <v>693</v>
@@ -16713,7 +16716,7 @@
         <v>98674</v>
       </c>
       <c r="I488" s="1" t="s">
-        <v>260</v>
+        <v>46</v>
       </c>
     </row>
     <row r="489" spans="1:9" x14ac:dyDescent="0.35">
@@ -16721,7 +16724,7 @@
         <v>153</v>
       </c>
       <c r="B489" s="3" t="s">
-        <v>241</v>
+        <v>35</v>
       </c>
       <c r="C489" s="1" t="s">
         <v>7</v>
@@ -16742,24 +16745,24 @@
         <v>98674</v>
       </c>
       <c r="I489" s="1" t="s">
-        <v>17</v>
+        <v>260</v>
       </c>
     </row>
     <row r="490" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A490" s="3" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="B490" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="C490" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D490" t="s">
+        <v>11</v>
+      </c>
+      <c r="E490" t="s">
         <v>695</v>
-      </c>
-      <c r="C490" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D490" t="s">
-        <v>23</v>
-      </c>
-      <c r="E490" t="s">
-        <v>694</v>
       </c>
       <c r="F490" t="s">
         <v>243</v>
@@ -16771,27 +16774,27 @@
         <v>98674</v>
       </c>
       <c r="I490" s="1" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
     </row>
     <row r="491" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A491" s="3" t="s">
-        <v>280</v>
+        <v>149</v>
       </c>
       <c r="B491" s="3" t="s">
-        <v>25</v>
+        <v>696</v>
       </c>
       <c r="C491" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D491" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="E491" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="F491" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="G491" t="s">
         <v>11</v>
@@ -16800,15 +16803,15 @@
         <v>98674</v>
       </c>
       <c r="I491" s="1" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="492" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A492" s="3" t="s">
-        <v>28</v>
+        <v>280</v>
       </c>
       <c r="B492" s="3" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="C492" s="1" t="s">
         <v>7</v>
@@ -16820,7 +16823,7 @@
         <v>697</v>
       </c>
       <c r="F492" t="s">
-        <v>16</v>
+        <v>240</v>
       </c>
       <c r="G492" t="s">
         <v>11</v>
@@ -16834,10 +16837,10 @@
     </row>
     <row r="493" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A493" s="3" t="s">
-        <v>153</v>
+        <v>28</v>
       </c>
       <c r="B493" s="3" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="C493" s="1" t="s">
         <v>7</v>
@@ -16849,7 +16852,7 @@
         <v>698</v>
       </c>
       <c r="F493" t="s">
-        <v>270</v>
+        <v>16</v>
       </c>
       <c r="G493" t="s">
         <v>11</v>
@@ -16858,7 +16861,7 @@
         <v>98674</v>
       </c>
       <c r="I493" s="1" t="s">
-        <v>260</v>
+        <v>17</v>
       </c>
     </row>
     <row r="494" spans="1:9" x14ac:dyDescent="0.35">
@@ -16866,7 +16869,7 @@
         <v>153</v>
       </c>
       <c r="B494" s="3" t="s">
-        <v>265</v>
+        <v>25</v>
       </c>
       <c r="C494" s="1" t="s">
         <v>7</v>
@@ -16878,7 +16881,7 @@
         <v>699</v>
       </c>
       <c r="F494" t="s">
-        <v>240</v>
+        <v>270</v>
       </c>
       <c r="G494" t="s">
         <v>11</v>
@@ -16887,7 +16890,7 @@
         <v>98674</v>
       </c>
       <c r="I494" s="1" t="s">
-        <v>17</v>
+        <v>260</v>
       </c>
     </row>
     <row r="495" spans="1:9" x14ac:dyDescent="0.35">
@@ -16895,7 +16898,7 @@
         <v>153</v>
       </c>
       <c r="B495" s="3" t="s">
-        <v>25</v>
+        <v>265</v>
       </c>
       <c r="C495" s="1" t="s">
         <v>7</v>
@@ -16921,20 +16924,20 @@
     </row>
     <row r="496" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A496" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="B496" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C496" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D496" t="s">
+        <v>11</v>
+      </c>
+      <c r="E496" t="s">
         <v>701</v>
       </c>
-      <c r="B496" s="3" t="s">
-        <v>702</v>
-      </c>
-      <c r="C496" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D496" t="s">
-        <v>11</v>
-      </c>
-      <c r="E496" t="s">
-        <v>703</v>
-      </c>
       <c r="F496" t="s">
         <v>240</v>
       </c>
@@ -16945,27 +16948,27 @@
         <v>98674</v>
       </c>
       <c r="I496" s="1" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
     </row>
     <row r="497" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A497" s="3" t="s">
+        <v>702</v>
+      </c>
+      <c r="B497" s="3" t="s">
+        <v>703</v>
+      </c>
+      <c r="C497" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D497" t="s">
+        <v>11</v>
+      </c>
+      <c r="E497" t="s">
         <v>704</v>
       </c>
-      <c r="B497" s="3" t="s">
-        <v>257</v>
-      </c>
-      <c r="C497" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D497" t="s">
-        <v>11</v>
-      </c>
-      <c r="E497" t="s">
-        <v>705</v>
-      </c>
       <c r="F497" t="s">
-        <v>270</v>
+        <v>240</v>
       </c>
       <c r="G497" t="s">
         <v>11</v>
@@ -16974,15 +16977,15 @@
         <v>98674</v>
       </c>
       <c r="I497" s="1" t="s">
-        <v>249</v>
+        <v>12</v>
       </c>
     </row>
     <row r="498" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A498" s="3" t="s">
-        <v>153</v>
+        <v>705</v>
       </c>
       <c r="B498" s="3" t="s">
-        <v>25</v>
+        <v>257</v>
       </c>
       <c r="C498" s="1" t="s">
         <v>7</v>
@@ -16994,7 +16997,7 @@
         <v>706</v>
       </c>
       <c r="F498" t="s">
-        <v>240</v>
+        <v>270</v>
       </c>
       <c r="G498" t="s">
         <v>11</v>
@@ -17008,10 +17011,10 @@
     </row>
     <row r="499" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A499" s="3" t="s">
-        <v>393</v>
+        <v>153</v>
       </c>
       <c r="B499" s="3" t="s">
-        <v>257</v>
+        <v>25</v>
       </c>
       <c r="C499" s="1" t="s">
         <v>7</v>
@@ -17023,7 +17026,7 @@
         <v>707</v>
       </c>
       <c r="F499" t="s">
-        <v>16</v>
+        <v>240</v>
       </c>
       <c r="G499" t="s">
         <v>11</v>
@@ -17032,15 +17035,15 @@
         <v>98674</v>
       </c>
       <c r="I499" s="1" t="s">
-        <v>260</v>
+        <v>249</v>
       </c>
     </row>
     <row r="500" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A500" s="3" t="s">
-        <v>332</v>
+        <v>393</v>
       </c>
       <c r="B500" s="3" t="s">
-        <v>156</v>
+        <v>257</v>
       </c>
       <c r="C500" s="1" t="s">
         <v>7</v>
@@ -17049,7 +17052,7 @@
         <v>11</v>
       </c>
       <c r="E500" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="F500" t="s">
         <v>16</v>
@@ -17061,15 +17064,15 @@
         <v>98674</v>
       </c>
       <c r="I500" s="1" t="s">
-        <v>249</v>
+        <v>260</v>
       </c>
     </row>
     <row r="501" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A501" s="3" t="s">
-        <v>13</v>
+        <v>332</v>
       </c>
       <c r="B501" s="3" t="s">
-        <v>30</v>
+        <v>156</v>
       </c>
       <c r="C501" s="1" t="s">
         <v>7</v>
@@ -17081,7 +17084,7 @@
         <v>708</v>
       </c>
       <c r="F501" t="s">
-        <v>243</v>
+        <v>16</v>
       </c>
       <c r="G501" t="s">
         <v>11</v>
@@ -17090,15 +17093,15 @@
         <v>98674</v>
       </c>
       <c r="I501" s="1" t="s">
-        <v>17</v>
+        <v>249</v>
       </c>
     </row>
     <row r="502" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A502" s="3" t="s">
-        <v>153</v>
+        <v>13</v>
       </c>
       <c r="B502" s="3" t="s">
-        <v>241</v>
+        <v>30</v>
       </c>
       <c r="C502" s="1" t="s">
         <v>7</v>
@@ -17110,7 +17113,7 @@
         <v>709</v>
       </c>
       <c r="F502" t="s">
-        <v>270</v>
+        <v>243</v>
       </c>
       <c r="G502" t="s">
         <v>11</v>
@@ -17127,7 +17130,7 @@
         <v>153</v>
       </c>
       <c r="B503" s="3" t="s">
-        <v>14</v>
+        <v>241</v>
       </c>
       <c r="C503" s="1" t="s">
         <v>7</v>
@@ -17139,7 +17142,7 @@
         <v>710</v>
       </c>
       <c r="F503" t="s">
-        <v>243</v>
+        <v>270</v>
       </c>
       <c r="G503" t="s">
         <v>11</v>
@@ -17148,7 +17151,7 @@
         <v>98674</v>
       </c>
       <c r="I503" s="1" t="s">
-        <v>260</v>
+        <v>17</v>
       </c>
     </row>
     <row r="504" spans="1:9" x14ac:dyDescent="0.35">
@@ -17156,7 +17159,7 @@
         <v>153</v>
       </c>
       <c r="B504" s="3" t="s">
-        <v>241</v>
+        <v>14</v>
       </c>
       <c r="C504" s="1" t="s">
         <v>7</v>
@@ -17168,7 +17171,7 @@
         <v>711</v>
       </c>
       <c r="F504" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="G504" t="s">
         <v>11</v>
@@ -17185,7 +17188,7 @@
         <v>153</v>
       </c>
       <c r="B505" s="3" t="s">
-        <v>14</v>
+        <v>241</v>
       </c>
       <c r="C505" s="1" t="s">
         <v>7</v>
@@ -17206,15 +17209,15 @@
         <v>98674</v>
       </c>
       <c r="I505" s="1" t="s">
-        <v>237</v>
+        <v>260</v>
       </c>
     </row>
     <row r="506" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A506" s="3" t="s">
-        <v>24</v>
+        <v>153</v>
       </c>
       <c r="B506" s="3" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="C506" s="1" t="s">
         <v>7</v>
@@ -17235,15 +17238,15 @@
         <v>98674</v>
       </c>
       <c r="I506" s="1" t="s">
-        <v>260</v>
+        <v>237</v>
       </c>
     </row>
     <row r="507" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A507" s="3" t="s">
-        <v>363</v>
+        <v>24</v>
       </c>
       <c r="B507" s="3" t="s">
-        <v>168</v>
+        <v>25</v>
       </c>
       <c r="C507" s="1" t="s">
         <v>7</v>
@@ -17255,7 +17258,7 @@
         <v>714</v>
       </c>
       <c r="F507" t="s">
-        <v>16</v>
+        <v>240</v>
       </c>
       <c r="G507" t="s">
         <v>11</v>
@@ -17264,15 +17267,15 @@
         <v>98674</v>
       </c>
       <c r="I507" s="1" t="s">
-        <v>20</v>
+        <v>260</v>
       </c>
     </row>
     <row r="508" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A508" s="3" t="s">
-        <v>18</v>
+        <v>363</v>
       </c>
       <c r="B508" s="3" t="s">
-        <v>238</v>
+        <v>168</v>
       </c>
       <c r="C508" s="1" t="s">
         <v>7</v>
@@ -17281,10 +17284,10 @@
         <v>11</v>
       </c>
       <c r="E508" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="F508" t="s">
-        <v>715</v>
+        <v>16</v>
       </c>
       <c r="G508" t="s">
         <v>11</v>
@@ -17298,10 +17301,10 @@
     </row>
     <row r="509" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A509" s="3" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="B509" s="3" t="s">
-        <v>25</v>
+        <v>238</v>
       </c>
       <c r="C509" s="1" t="s">
         <v>7</v>
@@ -17310,11 +17313,11 @@
         <v>11</v>
       </c>
       <c r="E509" t="s">
+        <v>715</v>
+      </c>
+      <c r="F509" t="s">
         <v>716</v>
       </c>
-      <c r="F509" t="s">
-        <v>243</v>
-      </c>
       <c r="G509" t="s">
         <v>11</v>
       </c>
@@ -17322,15 +17325,15 @@
         <v>98674</v>
       </c>
       <c r="I509" s="1" t="s">
-        <v>249</v>
+        <v>20</v>
       </c>
     </row>
     <row r="510" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A510" s="3" t="s">
-        <v>153</v>
+        <v>24</v>
       </c>
       <c r="B510" s="3" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="C510" s="1" t="s">
         <v>7</v>
@@ -17342,7 +17345,7 @@
         <v>717</v>
       </c>
       <c r="F510" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="G510" t="s">
         <v>11</v>
@@ -17351,7 +17354,7 @@
         <v>98674</v>
       </c>
       <c r="I510" s="1" t="s">
-        <v>17</v>
+        <v>249</v>
       </c>
     </row>
     <row r="511" spans="1:9" x14ac:dyDescent="0.35">
@@ -17359,7 +17362,7 @@
         <v>153</v>
       </c>
       <c r="B511" s="3" t="s">
-        <v>241</v>
+        <v>35</v>
       </c>
       <c r="C511" s="1" t="s">
         <v>7</v>
@@ -17371,7 +17374,7 @@
         <v>718</v>
       </c>
       <c r="F511" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="G511" t="s">
         <v>11</v>
@@ -17380,15 +17383,15 @@
         <v>98674</v>
       </c>
       <c r="I511" s="1" t="s">
-        <v>237</v>
+        <v>17</v>
       </c>
     </row>
     <row r="512" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A512" s="3" t="s">
-        <v>28</v>
+        <v>153</v>
       </c>
       <c r="B512" s="3" t="s">
-        <v>35</v>
+        <v>241</v>
       </c>
       <c r="C512" s="1" t="s">
         <v>7</v>
@@ -17400,37 +17403,66 @@
         <v>719</v>
       </c>
       <c r="F512" t="s">
+        <v>243</v>
+      </c>
+      <c r="G512" t="s">
+        <v>11</v>
+      </c>
+      <c r="H512">
+        <v>98674</v>
+      </c>
+      <c r="I512" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="513" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A513" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B513" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C513" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D513" t="s">
+        <v>11</v>
+      </c>
+      <c r="E513" t="s">
+        <v>720</v>
+      </c>
+      <c r="F513" t="s">
         <v>16</v>
       </c>
-      <c r="G512" t="s">
-        <v>11</v>
-      </c>
-      <c r="H512">
-        <v>98674</v>
-      </c>
-      <c r="I512" s="1" t="s">
+      <c r="G513" t="s">
+        <v>11</v>
+      </c>
+      <c r="H513">
+        <v>98674</v>
+      </c>
+      <c r="I513" s="1" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="513" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A513" s="6" t="s">
-        <v>720</v>
-      </c>
-      <c r="B513" s="6"/>
-      <c r="C513" s="6"/>
-      <c r="D513" t="s">
-        <v>11</v>
-      </c>
-      <c r="E513" t="s">
-        <v>11</v>
-      </c>
-      <c r="F513" t="s">
-        <v>11</v>
-      </c>
-      <c r="G513" t="s">
-        <v>11</v>
-      </c>
-      <c r="H513" t="s">
+    <row r="514" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A514" s="6" t="s">
+        <v>721</v>
+      </c>
+      <c r="B514" s="6"/>
+      <c r="C514" s="6"/>
+      <c r="D514" t="s">
+        <v>11</v>
+      </c>
+      <c r="E514" t="s">
+        <v>11</v>
+      </c>
+      <c r="F514" t="s">
+        <v>11</v>
+      </c>
+      <c r="G514" t="s">
+        <v>11</v>
+      </c>
+      <c r="H514" t="s">
         <v>11</v>
       </c>
     </row>
@@ -17439,7 +17471,7 @@
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="D2:G2"/>
-    <mergeCell ref="A513:C513"/>
+    <mergeCell ref="A514:C514"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
